--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="27">
   <si>
     <t>Mat</t>
   </si>
@@ -83,6 +83,21 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MENDIZABAL</t>
+  </si>
+  <si>
+    <t>LEON</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>DANNA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -483,16 +498,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -506,16 +524,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.84999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -555,16 +576,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H5">
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -578,16 +602,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -601,16 +628,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H7">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -666,7 +696,7 @@
         <v>32</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="F2">
         <v>0</v>
@@ -689,7 +719,7 @@
         <v>33</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="F3">
         <v>0</v>
@@ -735,7 +765,7 @@
         <v>33</v>
       </c>
       <c r="E5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="F5">
         <v>0</v>
@@ -758,7 +788,7 @@
         <v>19</v>
       </c>
       <c r="E6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F6">
         <v>0</v>
@@ -781,7 +811,7 @@
         <v>32</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="F7">
         <v>0</v>
@@ -840,16 +870,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>32</v>
+        <v>3</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>90.63</v>
+      </c>
+      <c r="H2">
+        <v>7.5</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -863,16 +896,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>5</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>84.84999999999999</v>
+      </c>
+      <c r="H3">
+        <v>7.9</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -912,16 +948,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>2</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>31</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>93.94</v>
+      </c>
+      <c r="H5">
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -935,16 +974,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>78.95</v>
+      </c>
+      <c r="H6">
+        <v>7.9</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -958,16 +1000,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>5</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>84.38</v>
+      </c>
+      <c r="H7">
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -977,7 +1022,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1007,6 +1052,49 @@
         <v>21</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>20330051920099</v>
+      </c>
+      <c r="B2" t="s">
+        <v>22</v>
+      </c>
+      <c r="D2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>11</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
+      <c r="A3">
+        <v>19330051920202</v>
+      </c>
+      <c r="B3" t="s">
+        <v>23</v>
+      </c>
+      <c r="C3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D3" t="s">
+        <v>26</v>
+      </c>
+      <c r="E3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
@@ -1092,7 +1092,7 @@
         <v>13</v>
       </c>
       <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="76" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="30">
   <si>
     <t>Mat</t>
   </si>
@@ -88,13 +88,22 @@
     <t>MENDIZABAL</t>
   </si>
   <si>
+    <t>MIXCOHUA</t>
+  </si>
+  <si>
     <t>LEON</t>
   </si>
   <si>
+    <t>ZEPAHUA</t>
+  </si>
+  <si>
     <t>GONZALEZ</t>
   </si>
   <si>
     <t>ALDER ALBERTO</t>
+  </si>
+  <si>
+    <t>ALEXIS</t>
   </si>
   <si>
     <t>DANNA PAOLA</t>
@@ -1022,7 +1031,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1060,7 +1069,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
@@ -1074,16 +1083,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>19330051920202</v>
+        <v>19330051920207</v>
       </c>
       <c r="B3" t="s">
         <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1092,6 +1101,29 @@
         <v>13</v>
       </c>
       <c r="G3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7">
+      <c r="A4">
+        <v>19330051920202</v>
+      </c>
+      <c r="B4" t="s">
+        <v>24</v>
+      </c>
+      <c r="C4" t="s">
+        <v>26</v>
+      </c>
+      <c r="D4" t="s">
+        <v>29</v>
+      </c>
+      <c r="E4" t="s">
+        <v>9</v>
+      </c>
+      <c r="F4" t="s">
+        <v>13</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
     </row>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="81" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
   <si>
     <t>Mat</t>
   </si>
@@ -85,28 +85,22 @@
     <t>Reprobadas</t>
   </si>
   <si>
-    <t>MENDIZABAL</t>
+    <t>ALDUCIN</t>
   </si>
   <si>
     <t>MIXCOHUA</t>
   </si>
   <si>
-    <t>LEON</t>
+    <t>HERNANDEZ</t>
   </si>
   <si>
     <t>ZEPAHUA</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
-  </si>
-  <si>
-    <t>ALDER ALBERTO</t>
+    <t>YATZIRI NAOMI</t>
   </si>
   <si>
     <t>ALEXIS</t>
-  </si>
-  <si>
-    <t>DANNA PAOLA</t>
   </si>
 </sst>
 </file>
@@ -507,19 +501,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -533,19 +527,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -585,19 +579,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -611,19 +605,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -637,16 +631,16 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H7">
         <v>8.4</v>
@@ -702,16 +696,19 @@
         <v>32</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
+        <v>0</v>
+      </c>
+      <c r="F2">
         <v>32</v>
       </c>
-      <c r="E2">
-        <v>29</v>
-      </c>
-      <c r="F2">
-        <v>0</v>
-      </c>
       <c r="G2">
-        <v>0</v>
+        <v>100</v>
+      </c>
+      <c r="H2">
+        <v>7.4</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -725,16 +722,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E3">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="F3">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H3">
+        <v>7.8</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -748,16 +748,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>22</v>
+        <v>2</v>
       </c>
       <c r="E4">
+        <v>0</v>
+      </c>
+      <c r="F4">
         <v>20</v>
       </c>
-      <c r="F4">
-        <v>0</v>
-      </c>
       <c r="G4">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H4">
+        <v>9.800000000000001</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -771,16 +774,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>33</v>
+        <v>3</v>
       </c>
       <c r="E5">
-        <v>31</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="G5">
-        <v>0</v>
+        <v>90.91</v>
+      </c>
+      <c r="H5">
+        <v>9.4</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -794,16 +800,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>19</v>
+        <v>2</v>
       </c>
       <c r="E6">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="F6">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>0</v>
+        <v>89.47</v>
+      </c>
+      <c r="H6">
+        <v>7.7</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -817,16 +826,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>7</v>
       </c>
       <c r="E7">
-        <v>27</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="G7">
-        <v>0</v>
+        <v>78.13</v>
+      </c>
+      <c r="H7">
+        <v>8.699999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -879,19 +891,19 @@
         <v>32</v>
       </c>
       <c r="D2">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="G2">
-        <v>90.63</v>
+        <v>100</v>
       </c>
       <c r="H2">
-        <v>7.5</v>
+        <v>8</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -905,19 +917,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E3">
         <v>0</v>
       </c>
       <c r="F3">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G3">
-        <v>84.84999999999999</v>
+        <v>90.91</v>
       </c>
       <c r="H3">
-        <v>7.9</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -943,7 +955,7 @@
         <v>90.91</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>9.699999999999999</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -957,19 +969,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="G5">
-        <v>93.94</v>
+        <v>96.97</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -983,19 +995,19 @@
         <v>19</v>
       </c>
       <c r="D6">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="G6">
-        <v>78.95</v>
+        <v>89.47</v>
       </c>
       <c r="H6">
-        <v>7.9</v>
+        <v>7.8</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1009,19 +1021,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E7">
         <v>0</v>
       </c>
       <c r="F7">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="G7">
-        <v>84.38</v>
+        <v>87.5</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1031,7 +1043,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G3"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1063,19 +1075,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920099</v>
+        <v>19330051920125</v>
       </c>
       <c r="B2" t="s">
         <v>22</v>
       </c>
+      <c r="C2" t="s">
+        <v>24</v>
+      </c>
       <c r="D2" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E2" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="G2">
         <v>2</v>
@@ -1092,7 +1107,7 @@
         <v>25</v>
       </c>
       <c r="D3" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E3" t="s">
         <v>9</v>
@@ -1102,29 +1117,6 @@
       </c>
       <c r="G3">
         <v>2</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4">
-        <v>19330051920202</v>
-      </c>
-      <c r="B4" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="D4" t="s">
-        <v>29</v>
-      </c>
-      <c r="E4" t="s">
-        <v>9</v>
-      </c>
-      <c r="F4" t="s">
-        <v>13</v>
-      </c>
-      <c r="G4">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
   <si>
     <t>Mat</t>
   </si>
@@ -88,19 +88,10 @@
     <t>ALDUCIN</t>
   </si>
   <si>
-    <t>MIXCOHUA</t>
-  </si>
-  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
-    <t>ZEPAHUA</t>
-  </si>
-  <si>
     <t>YATZIRI NAOMI</t>
-  </si>
-  <si>
-    <t>ALEXIS</t>
   </si>
 </sst>
 </file>
@@ -579,16 +570,16 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>9.4</v>
@@ -774,16 +765,16 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H5">
         <v>9.4</v>
@@ -903,7 +894,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -929,7 +920,7 @@
         <v>90.91</v>
       </c>
       <c r="H3">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -969,19 +960,19 @@
         <v>33</v>
       </c>
       <c r="D5">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E5">
         <v>0</v>
       </c>
       <c r="F5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="G5">
-        <v>96.97</v>
+        <v>100</v>
       </c>
       <c r="H5">
-        <v>9.6</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -1043,7 +1034,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1081,10 +1072,10 @@
         <v>22</v>
       </c>
       <c r="C2" t="s">
+        <v>23</v>
+      </c>
+      <c r="D2" t="s">
         <v>24</v>
-      </c>
-      <c r="D2" t="s">
-        <v>26</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
@@ -1093,30 +1084,7 @@
         <v>12</v>
       </c>
       <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3">
-        <v>19330051920207</v>
-      </c>
-      <c r="B3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C3" t="s">
-        <v>25</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>9</v>
-      </c>
-      <c r="F3" t="s">
-        <v>13</v>
-      </c>
-      <c r="G3">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
+++ b/docentes/Jiménez Nieto Enrique - Estadisticos 20212.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="25">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="22">
   <si>
     <t>Mat</t>
   </si>
@@ -83,15 +83,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>ALDUCIN</t>
-  </si>
-  <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
-    <t>YATZIRI NAOMI</t>
   </si>
 </sst>
 </file>
@@ -518,19 +509,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -544,19 +535,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -596,10 +587,10 @@
         <v>19</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>2</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>17</v>
@@ -608,7 +599,7 @@
         <v>89.47</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -622,19 +613,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="G7">
-        <v>87.5</v>
+        <v>96.88</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -713,19 +704,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -739,19 +730,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.800000000000001</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -791,10 +782,10 @@
         <v>19</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>2</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>17</v>
@@ -803,7 +794,7 @@
         <v>89.47</v>
       </c>
       <c r="H6">
-        <v>7.7</v>
+        <v>7.4</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -817,19 +808,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>78.13</v>
+        <v>93.75</v>
       </c>
       <c r="H7">
-        <v>8.699999999999999</v>
+        <v>8.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -894,7 +885,7 @@
         <v>100</v>
       </c>
       <c r="H2">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:8">
@@ -908,19 +899,19 @@
         <v>33</v>
       </c>
       <c r="D3">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F3">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="G3">
-        <v>90.91</v>
+        <v>96.97</v>
       </c>
       <c r="H3">
-        <v>8.199999999999999</v>
+        <v>8.1</v>
       </c>
     </row>
     <row r="4" spans="1:8">
@@ -934,19 +925,19 @@
         <v>22</v>
       </c>
       <c r="D4">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>0</v>
       </c>
       <c r="F4">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="G4">
-        <v>90.91</v>
+        <v>100</v>
       </c>
       <c r="H4">
-        <v>9.699999999999999</v>
+        <v>9.5</v>
       </c>
     </row>
     <row r="5" spans="1:8">
@@ -972,7 +963,7 @@
         <v>100</v>
       </c>
       <c r="H5">
-        <v>9.5</v>
+        <v>9.6</v>
       </c>
     </row>
     <row r="6" spans="1:8">
@@ -986,10 +977,10 @@
         <v>19</v>
       </c>
       <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6">
         <v>2</v>
-      </c>
-      <c r="E6">
-        <v>0</v>
       </c>
       <c r="F6">
         <v>17</v>
@@ -998,7 +989,7 @@
         <v>89.47</v>
       </c>
       <c r="H6">
-        <v>7.8</v>
+        <v>7.5</v>
       </c>
     </row>
     <row r="7" spans="1:8">
@@ -1012,19 +1003,19 @@
         <v>32</v>
       </c>
       <c r="D7">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="E7">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="G7">
-        <v>87.5</v>
+        <v>93.75</v>
       </c>
       <c r="H7">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1025,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -1064,29 +1055,6 @@
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>19330051920125</v>
-      </c>
-      <c r="B2" t="s">
-        <v>22</v>
-      </c>
-      <c r="C2" t="s">
-        <v>23</v>
-      </c>
-      <c r="D2" t="s">
-        <v>24</v>
-      </c>
-      <c r="E2" t="s">
-        <v>9</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
-      </c>
-      <c r="G2">
-        <v>1</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
